--- a/מערכות שעות - לפי בתים.xlsx
+++ b/מערכות שעות - לפי בתים.xlsx
@@ -12003,157 +12003,157 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>דניאל צאל</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>דניאל</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>מחנך ג דניאל</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>חסאן סראחן</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>חסן</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>ספורט יסודי · מגמות (ליווי ימית, ספורט ט)</t>
         </is>
       </c>
-      <c r="E3" s="20" t="n">
+      <c r="E4" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="20" t="n">
+      <c r="F4" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="G3" s="20" t="inlineStr"/>
-      <c r="H3" s="20" t="n">
+      <c r="G4" s="20" t="inlineStr"/>
+      <c r="H4" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="I3" s="20" t="n">
+      <c r="I4" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="J3" s="20" t="n">
+      <c r="J4" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="K3" s="20" t="n">
+      <c r="K4" s="20" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>דניאל צאל</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>דניאל</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>אביטל בוארון</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>אביטל</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>רביעי</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>מחנך ג דניאל</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ב אביטל</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="n">
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="J5" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>מרים</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>מרים</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>ערבית ז+ח+ט · סטאז עברית ביסודי (13 שעות, דגש א-ג)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="n">
+      <c r="E6" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="F5" s="20" t="n">
+      <c r="F6" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="n">
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="J5" s="20" t="n">
+      <c r="J6" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="K5" s="20" t="n">
+      <c r="K6" s="20" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>אביטל בוארון</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>אביטל</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>רביעי</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ב אביטל</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -12231,176 +12231,176 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>אינס אלקבץ</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>אינס</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת ד אינס</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="J9" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>תמיר באום</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>תמיר</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>מחנך ט תמיר · תנ"ך ט · היסטוריה ט · אזרחות ט · 4 שעות בכיתות ו · ליווי מגמות חמישי</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>דליה מרקוס</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>דליה</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>חמישי</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>מחנכת ג דליה</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E11" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="n">
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J11" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="K11" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>אינס אלקבץ</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>אינס</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>שלישי</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ד אינס</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="n">
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>סימה דוד</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>סימה</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>יסודי</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
-      <c r="I10" s="20" t="n">
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="J10" s="20" t="n">
+      <c r="J12" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="K10" s="20" t="n">
+      <c r="K12" s="20" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>סימה דוד</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>סימה</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>יסודי</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="F11" s="20" t="inlineStr"/>
-      <c r="G11" s="20" t="inlineStr"/>
-      <c r="H11" s="20" t="inlineStr"/>
-      <c r="I11" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="J11" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="K11" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>תמיר באום</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>תמיר</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>שלישי</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>מחנך ט תמיר · תנ"ך ט · היסטוריה ט · אזרחות ט · 4 שעות בכיתות ו · ליווי מגמות חמישי</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>מירי בן עמי קריימר</t>
+          <t>פנינה קרפטי</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>מירי</t>
+          <t>פנינה</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>חמישי</t>
+          <t>שני</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>מחנכת ד מירי</t>
+          <t>מחנכת א פנינה</t>
         </is>
       </c>
       <c r="E13" s="20" t="n">
@@ -12420,229 +12420,229 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>מירי בן עמי קריימר</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>מירי</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת ד מירי</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
+      <c r="H14" s="20" t="inlineStr"/>
+      <c r="I14" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>לייה גור</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>לייה</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>רביעי</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>מחנכת ג לייה · תנ"ך ח (כפול רצוף)</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E15" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="n">
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="J15" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="K15" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>פנינה קרפטי</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>פנינה</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>אסיף בניש</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>אסיף</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>מחנך ט אסיף · שפה ט · מדעים ז · חינוך פיננסי ט · מגמת יזמות</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>גלית בצלאל</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>שני</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת א פנינה</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="20" t="inlineStr"/>
-      <c r="H15" s="20" t="inlineStr"/>
-      <c r="I15" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="K15" s="20" t="n">
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת ח · אנגלית ח+ט · שיעורים עם ארז בז</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" s="20" t="inlineStr"/>
+      <c r="H17" s="20" t="inlineStr"/>
+      <c r="I17" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="K17" s="20" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>נעמי קציר</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>נעמי</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>דני יהב בראון</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>דני</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>שלישי</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>מחנך ה דני (20 שעות)</t>
         </is>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E19" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
-      <c r="H16" s="20" t="inlineStr"/>
-      <c r="I16" s="20" t="n">
+      <c r="F19" s="20" t="inlineStr"/>
+      <c r="G19" s="20" t="inlineStr"/>
+      <c r="H19" s="20" t="inlineStr"/>
+      <c r="I19" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="J16" s="20" t="n">
+      <c r="J19" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="K16" s="20" t="n">
+      <c r="K19" s="20" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>נעמי קציר</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>נעמי</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>גלית בצלאל</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>גלית</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>שני</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ח · אנגלית ח+ט · שיעורים עם ארז בז</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr"/>
-      <c r="F18" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="G18" s="20" t="inlineStr"/>
-      <c r="H18" s="20" t="inlineStr"/>
-      <c r="I18" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="J18" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="K18" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>אסיף בניש</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>אסיף</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>מחנך ט אסיף · שפה ט · מדעים ז · חינוך פיננסי ט · מגמת יזמות</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -12798,30 +12798,32 @@
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>הילית בן מאיר שטרן</t>
+          <t>יעל ליפשיץ</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>הילית</t>
+          <t>יעל</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>חמישי, שישי</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>תל"ן פיסול</t>
+          <t>תל"ן בישול (ד-ו) · מגמה</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr"/>
       <c r="F24" s="20" t="inlineStr"/>
       <c r="G24" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="H24" s="20" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="H24" s="20" t="n">
+        <v>4</v>
+      </c>
       <c r="I24" s="20" t="n">
         <v>16</v>
       </c>
@@ -12835,32 +12837,30 @@
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>יעל ליפשיץ</t>
+          <t>פאני קרוטמן</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>יעל</t>
+          <t>פאני</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>שלישי</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>תל"ן בישול (ד-ו) · מגמה</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr"/>
+          <t>ספורט יסודי (פעמיים בשבוע לכיתה, בימים שונים)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>16</v>
+      </c>
       <c r="F25" s="20" t="inlineStr"/>
-      <c r="G25" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="H25" s="20" t="n">
-        <v>4</v>
-      </c>
+      <c r="G25" s="20" t="inlineStr"/>
+      <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="n">
         <v>16</v>
       </c>
@@ -12874,12 +12874,12 @@
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>יפעת גולדבלט</t>
+          <t>הילית בן מאיר שטרן</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>יפעת</t>
+          <t>הילית</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>תל"ן חינוך סביבתי</t>
+          <t>תל"ן פיסול</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr"/>
@@ -12911,29 +12911,29 @@
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>פאני קרוטמן</t>
+          <t>יפעת גולדבלט</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>פאני</t>
+          <t>יפעת</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>שלישי</t>
+          <t>חמישי, שישי</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>ספורט יסודי (פעמיים בשבוע לכיתה, בימים שונים)</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="n">
+          <t>תל"ן חינוך סביבתי</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
+      <c r="G27" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="F27" s="20" t="inlineStr"/>
-      <c r="G27" s="20" t="inlineStr"/>
       <c r="H27" s="20" t="inlineStr"/>
       <c r="I27" s="20" t="n">
         <v>16</v>
@@ -12985,22 +12985,20 @@
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>צבי טולצ'ינסקי</t>
+          <t>אבי קרן צבי</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>צבי</t>
+          <t>אבי קרן צבי</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr"/>
       <c r="D29" s="19" t="inlineStr"/>
       <c r="E29" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>9</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F29" s="20" t="inlineStr"/>
       <c r="G29" s="20" t="inlineStr"/>
       <c r="H29" s="20" t="inlineStr"/>
       <c r="I29" s="20" t="n">
@@ -13016,20 +13014,22 @@
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>אבי קרן צבי</t>
+          <t>צבי טולצ'ינסקי</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>אבי קרן צבי</t>
+          <t>צבי</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr"/>
       <c r="D30" s="19" t="inlineStr"/>
       <c r="E30" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="F30" s="20" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="F30" s="20" t="n">
+        <v>9</v>
+      </c>
       <c r="G30" s="20" t="inlineStr"/>
       <c r="H30" s="20" t="inlineStr"/>
       <c r="I30" s="20" t="n">
@@ -13232,22 +13232,22 @@
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>הדר קורצויל</t>
+          <t>ארז</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>הדר</t>
+          <t>ארז</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>שישי</t>
+          <t>ראשון, שני, שלישי, שישי</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>מתמטיקה ז (8 שעות, 2-3 ימים)</t>
+          <t>אנגלית ז (רביעי+חמישי, 2+2)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr"/>
@@ -13269,22 +13269,22 @@
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>ארז</t>
+          <t>הדר קורצויל</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>ארז</t>
+          <t>הדר</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>ראשון, שני, שלישי, שישי</t>
+          <t>שישי</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>אנגלית ז (רביעי+חמישי, 2+2)</t>
+          <t>מתמטיקה ז (8 שעות, 2-3 ימים)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr"/>

--- a/מערכות שעות - לפי בתים.xlsx
+++ b/מערכות שעות - לפי בתים.xlsx
@@ -12083,77 +12083,75 @@
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>אביטל בוארון</t>
+          <t>יערה שיכט</t>
         </is>
       </c>
       <c r="B5" s="18" t="inlineStr">
         <is>
-          <t>אביטל</t>
+          <t>יערה</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>רביעי</t>
+          <t>שני</t>
         </is>
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>מחנכת ב אביטל</t>
+          <t>מחנכת ב יערה</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
       <c r="I5" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K5" s="4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>אביטל בוארון</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>אביטל</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ב אביטל</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K6" s="4" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>מרים</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>מרים</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>ערבית ז+ח+ט · סטאז עברית ביסודי (13 שעות, דגש א-ג)</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="F6" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="J6" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="K6" s="20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -12194,40 +12192,42 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>יערה שיכט</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>יערה</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>שני</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ב יערה</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="J8" s="4" t="n">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>מרים</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>מרים</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>ערבית ז+ח+ט · סטאז עברית ביסודי (13 שעות, דגש א-ג)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="20" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
+      <c r="I8" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="K8" s="4" t="n">
-        <v>4</v>
+      <c r="J8" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="K8" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -12268,73 +12268,73 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>תמיר באום</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>תמיר</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>שלישי</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>מחנך ט תמיר · תנ"ך ט · היסטוריה ט · אזרחות ט · 4 שעות בכיתות ו · ליווי מגמות חמישי</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="J10" s="4" t="n">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>סימה דוד</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>סימה</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>יסודי</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="K10" s="4" t="n">
-        <v>1</v>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="J10" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="K10" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>דליה מרקוס</t>
+          <t>תמיר באום</t>
         </is>
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>דליה</t>
+          <t>תמיר</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>חמישי</t>
+          <t>שלישי</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>מחנכת ג דליה</t>
+          <t>מחנך ט תמיר · תנ"ך ט · היסטוריה ט · אזרחות ט · 4 שעות בכיתות ו · ליווי מגמות חמישי</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="I11" s="4" t="n">
         <v>23</v>
       </c>
@@ -12346,61 +12346,61 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>סימה דוד</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>סימה</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>יסודי</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="n">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>דליה מרקוס</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>דליה</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ג דליה</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J12" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>0</v>
+      <c r="K12" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>פנינה קרפטי</t>
+          <t>מירי בן עמי קריימר</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>פנינה</t>
+          <t>מירי</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>שני</t>
+          <t>חמישי</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>מחנכת א פנינה</t>
+          <t>מחנכת ד מירי</t>
         </is>
       </c>
       <c r="E13" s="20" t="n">
@@ -12422,22 +12422,22 @@
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>מירי בן עמי קריימר</t>
+          <t>פנינה קרפטי</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>מירי</t>
+          <t>פנינה</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>חמישי</t>
+          <t>שני</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>מחנכת ד מירי</t>
+          <t>מחנכת א פנינה</t>
         </is>
       </c>
       <c r="E14" s="20" t="n">
@@ -12496,143 +12496,145 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>דני יהב בראון</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>דני</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>מחנך ה דני (20 שעות)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
+      <c r="I16" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J16" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="K16" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>אסיף בניש</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>אסיף</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>מחנך ט אסיף · שפה ט · מדעים ז · חינוך פיננסי ט · מגמת יזמות</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="n">
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="n">
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I17" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="J17" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="K16" s="4" t="n">
+      <c r="K17" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>גלית בצלאל</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>גלית</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>שני</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ח · אנגלית ח+ט · שיעורים עם ארז בז</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr"/>
-      <c r="F17" s="20" t="n">
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>אלי אליהו מור</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>אלי</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>מנהל החטיבה · מחנך ז אלי (8 שעות) · תנ"ך והיסטוריה ז · היסטוריה+גיאוגרפיה ח · מגמת יזמות</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="G18" s="20" t="inlineStr"/>
+      <c r="H18" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="G17" s="20" t="inlineStr"/>
-      <c r="H17" s="20" t="inlineStr"/>
-      <c r="I17" s="20" t="n">
+      <c r="J18" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="J17" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="K17" s="20" t="n">
+      <c r="K18" s="20" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>נעמי קציר</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>נעמי</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>דני יהב בראון</t>
+          <t>גלית בצלאל</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>דני</t>
+          <t>גלית</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>שלישי</t>
+          <t>שני</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>מחנך ה דני (20 שעות)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="n">
+          <t>מחנכת ח · אנגלית ח+ט · שיעורים עם ארז בז</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="F19" s="20" t="inlineStr"/>
       <c r="G19" s="20" t="inlineStr"/>
       <c r="H19" s="20" t="inlineStr"/>
       <c r="I19" s="20" t="n">
@@ -12646,42 +12648,40 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>אלי אליהו מור</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>אלי</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>מנהל החטיבה · מחנך ז אלי (8 שעות) · תנ"ך והיסטוריה ז · היסטוריה+גיאוגרפיה ח · מגמת יזמות</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr"/>
-      <c r="F20" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="G20" s="20" t="inlineStr"/>
-      <c r="H20" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="20" t="n">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>נעמי קציר</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>נעמי</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J20" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="J20" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="K20" s="20" t="n">
-        <v>0</v>
+      <c r="K20" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -12837,29 +12837,29 @@
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>פאני קרוטמן</t>
+          <t>יפעת גולדבלט</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>פאני</t>
+          <t>יפעת</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>שלישי</t>
+          <t>חמישי, שישי</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>ספורט יסודי (פעמיים בשבוע לכיתה, בימים שונים)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="n">
+          <t>תל"ן חינוך סביבתי</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr"/>
+      <c r="F25" s="20" t="inlineStr"/>
+      <c r="G25" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="F25" s="20" t="inlineStr"/>
-      <c r="G25" s="20" t="inlineStr"/>
       <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="n">
         <v>16</v>
@@ -12874,29 +12874,29 @@
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>הילית בן מאיר שטרן</t>
+          <t>פאני קרוטמן</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>הילית</t>
+          <t>פאני</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>חמישי, שישי</t>
+          <t>שלישי</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>תל"ן פיסול</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr"/>
+          <t>ספורט יסודי (פעמיים בשבוע לכיתה, בימים שונים)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="n">
+        <v>16</v>
+      </c>
       <c r="F26" s="20" t="inlineStr"/>
-      <c r="G26" s="20" t="n">
-        <v>16</v>
-      </c>
+      <c r="G26" s="20" t="inlineStr"/>
       <c r="H26" s="20" t="inlineStr"/>
       <c r="I26" s="20" t="n">
         <v>16</v>
@@ -12911,12 +12911,12 @@
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>יפעת גולדבלט</t>
+          <t>הילית בן מאיר שטרן</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>יפעת</t>
+          <t>הילית</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>תל"ן חינוך סביבתי</t>
+          <t>תל"ן פיסול</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr"/>
@@ -13045,32 +13045,30 @@
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>חגית אבידן</t>
+          <t>שחר שלייסר</t>
         </is>
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>חגית</t>
+          <t>שחר</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>חמישי</t>
+          <t>ראשון, חמישי, שישי</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>תל"ן אומנות (א+ד) · מגמה</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="inlineStr"/>
+          <t>יסודי (שני-רביעי, לא בשעה אחרונה)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>10</v>
+      </c>
       <c r="F31" s="20" t="inlineStr"/>
-      <c r="G31" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="H31" s="20" t="n">
-        <v>2</v>
-      </c>
+      <c r="G31" s="20" t="inlineStr"/>
+      <c r="H31" s="20" t="inlineStr"/>
       <c r="I31" s="20" t="n">
         <v>10</v>
       </c>
@@ -13084,22 +13082,22 @@
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>שחר שלייסר</t>
+          <t>לי-אור שפירא</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>שחר</t>
+          <t>לי-אור</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>ראשון, חמישי, שישי</t>
+          <t>ראשון, רביעי, שישי</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>יסודי (שני-רביעי, לא בשעה אחרונה)</t>
+          <t>יסודי (עד 3 ימים)</t>
         </is>
       </c>
       <c r="E32" s="20" t="n">
@@ -13119,40 +13117,40 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>לי-אור שפירא</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>לי-אור</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>מאמי שימאזאקי</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>מאמי</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>יסודי (עד 3 ימים)</t>
-        </is>
-      </c>
-      <c r="E33" s="20" t="n">
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>מגמת אומנות בתנועה · רב מלל ח בחמישי 5-6</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F33" s="20" t="inlineStr"/>
-      <c r="G33" s="20" t="inlineStr"/>
-      <c r="H33" s="20" t="inlineStr"/>
-      <c r="I33" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="J33" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="K33" s="20" t="n">
-        <v>0</v>
+      <c r="K33" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -13193,61 +13191,63 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>מאמי שימאזאקי</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>מאמי</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>מגמת אומנות בתנועה · רב מלל ח בחמישי 5-6</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J35" s="4" t="n">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>חגית אבידן</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>חגית</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>תל"ן אומנות (א+ד) · מגמה</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr"/>
+      <c r="F35" s="20" t="inlineStr"/>
+      <c r="G35" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="K35" s="4" t="n">
-        <v>6</v>
+      <c r="J35" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="K35" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>ארז</t>
+          <t>הדר קורצויל</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>ארז</t>
+          <t>הדר</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>ראשון, שני, שלישי, שישי</t>
+          <t>שישי</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>אנגלית ז (רביעי+חמישי, 2+2)</t>
+          <t>מתמטיקה ז (8 שעות, 2-3 ימים)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr"/>
@@ -13269,22 +13269,22 @@
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>הדר קורצויל</t>
+          <t>ארז</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>הדר</t>
+          <t>ארז</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>שישי</t>
+          <t>ראשון, שני, שלישי, שישי</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>מתמטיקה ז (8 שעות, 2-3 ימים)</t>
+          <t>אנגלית ז (רביעי+חמישי, 2+2)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr"/>

--- a/מערכות שעות - לפי בתים.xlsx
+++ b/מערכות שעות - לפי בתים.xlsx
@@ -12003,231 +12003,231 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>חסאן סראחן</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>חסן</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>ספורט יסודי · מגמות (ליווי ימית, ספורט ט)</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" s="20" t="inlineStr"/>
+      <c r="H3" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="J3" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="K3" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>דניאל צאל</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>דניאל</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>רביעי</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>מחנך ג דניאל</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E4" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="n">
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J4" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="K4" s="4" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>חסאן סראחן</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>חסן</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>אנה זטרברג</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>אנה</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>ספורט יסודי · מגמות (ליווי ימית, ספורט ט)</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="n">
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת א אנה</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="J5" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="K5" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>מרים</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>מרים</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>ערבית ז+ח+ט · סטאז עברית ביסודי (13 שעות, דגש א-ג)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" s="20" t="inlineStr"/>
-      <c r="H4" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="I4" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="J4" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="K4" s="20" t="n">
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="J6" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="K6" s="20" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>יערה שיכט</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>יערה</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>שני</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>מחנכת ב יערה</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="n">
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J7" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K7" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>אביטל בוארון</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>אביטל</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>רביעי</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>מחנכת ב אביטל</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="n">
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J8" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K8" s="4" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>אנה זטרברג</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>אנה</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת א אנה</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="J7" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="K7" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>מרים</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>מרים</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>ערבית ז+ח+ט · סטאז עברית ביסודי (13 שעות, דגש א-ג)</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="F8" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="20" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
-      <c r="I8" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="J8" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="K8" s="20" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -12307,34 +12307,30 @@
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>תמיר באום</t>
+          <t>דליה מרקוס</t>
         </is>
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>תמיר</t>
+          <t>דליה</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>שלישי</t>
+          <t>חמישי</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>מחנך ט תמיר · תנ"ך ט · היסטוריה ט · אזרחות ט · 4 שעות בכיתות ו · ליווי מגמות חמישי</t>
+          <t>מחנכת ג דליה</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>15</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="n">
-        <v>4</v>
-      </c>
+      <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="4" t="n">
         <v>23</v>
       </c>
@@ -12348,30 +12344,34 @@
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>דליה מרקוס</t>
+          <t>תמיר באום</t>
         </is>
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>דליה</t>
+          <t>תמיר</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>חמישי</t>
+          <t>שלישי</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>מחנכת ג דליה</t>
+          <t>מחנך ט תמיר · תנ"ך ט · היסטוריה ט · אזרחות ט · 4 שעות בכיתות ו · ליווי מגמות חמישי</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="I12" s="4" t="n">
         <v>23</v>
       </c>
@@ -12385,22 +12385,22 @@
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>מירי בן עמי קריימר</t>
+          <t>פנינה קרפטי</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>מירי</t>
+          <t>פנינה</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>חמישי</t>
+          <t>שני</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>מחנכת ד מירי</t>
+          <t>מחנכת א פנינה</t>
         </is>
       </c>
       <c r="E13" s="20" t="n">
@@ -12422,22 +12422,22 @@
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>פנינה קרפטי</t>
+          <t>מירי בן עמי קריימר</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>פנינה</t>
+          <t>מירי</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>שני</t>
+          <t>חמישי</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>מחנכת א פנינה</t>
+          <t>מחנכת ד מירי</t>
         </is>
       </c>
       <c r="E14" s="20" t="n">
@@ -12533,110 +12533,108 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>אסיף בניש</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>אסיף</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>מחנך ט אסיף · שפה ט · מדעים ז · חינוך פיננסי ט · מגמת יזמות</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="n">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>גלית בצלאל</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>גלית</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>שני</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת ח · אנגלית ח+ט · שיעורים עם ארז בז</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr"/>
+      <c r="F17" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" s="20" t="inlineStr"/>
+      <c r="H17" s="20" t="inlineStr"/>
+      <c r="I17" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="K17" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>נעמי קציר</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>נעמי</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="J17" s="4" t="n">
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="K17" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>אלי אליהו מור</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>אלי</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>מנהל החטיבה · מחנך ז אלי (8 שעות) · תנ"ך והיסטוריה ז · היסטוריה+גיאוגרפיה ח · מגמת יזמות</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr"/>
-      <c r="F18" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="G18" s="20" t="inlineStr"/>
-      <c r="H18" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="J18" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="K18" s="20" t="n">
-        <v>0</v>
+      <c r="K18" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>גלית בצלאל</t>
+          <t>אלי אליהו מור</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>גלית</t>
+          <t>אלי</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>שני</t>
+          <t>שישי</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>מחנכת ח · אנגלית ח+ט · שיעורים עם ארז בז</t>
+          <t>מנהל החטיבה · מחנך ז אלי (8 שעות) · תנ"ך והיסטוריה ז · היסטוריה+גיאוגרפיה ח · מגמת יזמות</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr"/>
       <c r="F19" s="20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G19" s="20" t="inlineStr"/>
-      <c r="H19" s="20" t="inlineStr"/>
+      <c r="H19" s="20" t="n">
+        <v>2</v>
+      </c>
       <c r="I19" s="20" t="n">
         <v>20</v>
       </c>
@@ -12650,22 +12648,22 @@
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>נעמי קציר</t>
+          <t>אסיף בניש</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>נעמי</t>
+          <t>אסיף</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>חמישי</t>
+          <t>שישי</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
+          <t>מחנך ט אסיף · שפה ט · מדעים ז · חינוך פיננסי ט · מגמת יזמות</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -12673,110 +12671,112 @@
         <v>15</v>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="I20" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>תניה דניאלי</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>תניה</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ה תניה (ראשון+רביעי מ-10:00)</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="n">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>אורנה לוי</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>אורנה</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>שני, רביעי</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ו אורנה</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J21" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="20" t="inlineStr"/>
-      <c r="G21" s="20" t="inlineStr"/>
-      <c r="H21" s="20" t="inlineStr"/>
-      <c r="I21" s="20" t="n">
+      <c r="K21" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>צופיה חזון</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>צופיה</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>אנגלית ג · מקבילות עם אנה ופנינה · שישי בא אנה</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="J21" s="20" t="n">
+      <c r="F22" s="20" t="inlineStr"/>
+      <c r="G22" s="20" t="inlineStr"/>
+      <c r="H22" s="20" t="inlineStr"/>
+      <c r="I22" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="K21" s="20" t="n">
+      <c r="J22" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="K22" s="20" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>אורנה לוי</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>אורנה</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>שני, רביעי</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ו אורנה</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>צופיה חזון</t>
+          <t>תניה דניאלי</t>
         </is>
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>צופיה</t>
+          <t>תניה</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>חמישי</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
-          <t>אנגלית ג · מקבילות עם אנה ופנינה · שישי בא אנה</t>
+          <t>מחנכת ה תניה (ראשון+רביעי מ-10:00)</t>
         </is>
       </c>
       <c r="E23" s="20" t="n">
@@ -12837,29 +12837,29 @@
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>יפעת גולדבלט</t>
+          <t>פאני קרוטמן</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>יפעת</t>
+          <t>פאני</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>חמישי, שישי</t>
+          <t>שלישי</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>תל"ן חינוך סביבתי</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr"/>
+          <t>ספורט יסודי (פעמיים בשבוע לכיתה, בימים שונים)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>16</v>
+      </c>
       <c r="F25" s="20" t="inlineStr"/>
-      <c r="G25" s="20" t="n">
-        <v>16</v>
-      </c>
+      <c r="G25" s="20" t="inlineStr"/>
       <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="n">
         <v>16</v>
@@ -12874,29 +12874,29 @@
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>פאני קרוטמן</t>
+          <t>יפעת גולדבלט</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>פאני</t>
+          <t>יפעת</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>שלישי</t>
+          <t>חמישי, שישי</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>ספורט יסודי (פעמיים בשבוע לכיתה, בימים שונים)</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="n">
+          <t>תל"ן חינוך סביבתי</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr"/>
+      <c r="F26" s="20" t="inlineStr"/>
+      <c r="G26" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="F26" s="20" t="inlineStr"/>
-      <c r="G26" s="20" t="inlineStr"/>
       <c r="H26" s="20" t="inlineStr"/>
       <c r="I26" s="20" t="n">
         <v>16</v>
@@ -13045,30 +13045,32 @@
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>שחר שלייסר</t>
+          <t>חגית אבידן</t>
         </is>
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>שחר</t>
+          <t>חגית</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>ראשון, חמישי, שישי</t>
+          <t>חמישי</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>יסודי (שני-רביעי, לא בשעה אחרונה)</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="n">
-        <v>10</v>
-      </c>
+          <t>תל"ן אומנות (א+ד) · מגמה</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr"/>
       <c r="F31" s="20" t="inlineStr"/>
-      <c r="G31" s="20" t="inlineStr"/>
-      <c r="H31" s="20" t="inlineStr"/>
+      <c r="G31" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" s="20" t="n">
+        <v>2</v>
+      </c>
       <c r="I31" s="20" t="n">
         <v>10</v>
       </c>
@@ -13082,22 +13084,22 @@
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>לי-אור שפירא</t>
+          <t>שחר שלייסר</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>לי-אור</t>
+          <t>שחר</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>ראשון, רביעי, שישי</t>
+          <t>ראשון, חמישי, שישי</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>יסודי (עד 3 ימים)</t>
+          <t>יסודי (שני-רביעי, לא בשעה אחרונה)</t>
         </is>
       </c>
       <c r="E32" s="20" t="n">
@@ -13193,32 +13195,30 @@
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>חגית אבידן</t>
+          <t>לי-אור שפירא</t>
         </is>
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>חגית</t>
+          <t>לי-אור</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
         <is>
-          <t>חמישי</t>
+          <t>ראשון, רביעי, שישי</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>תל"ן אומנות (א+ד) · מגמה</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="inlineStr"/>
+          <t>יסודי (עד 3 ימים)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="n">
+        <v>10</v>
+      </c>
       <c r="F35" s="20" t="inlineStr"/>
-      <c r="G35" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="H35" s="20" t="n">
-        <v>2</v>
-      </c>
+      <c r="G35" s="20" t="inlineStr"/>
+      <c r="H35" s="20" t="inlineStr"/>
       <c r="I35" s="20" t="n">
         <v>10</v>
       </c>
@@ -13232,22 +13232,22 @@
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>הדר קורצויל</t>
+          <t>ארז</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>הדר</t>
+          <t>ארז</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>שישי</t>
+          <t>ראשון, שני, שלישי, שישי</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>מתמטיקה ז (8 שעות, 2-3 ימים)</t>
+          <t>אנגלית ז (רביעי+חמישי, 2+2)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr"/>
@@ -13269,22 +13269,22 @@
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>ארז</t>
+          <t>הדר קורצויל</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>ארז</t>
+          <t>הדר</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>ראשון, שני, שלישי, שישי</t>
+          <t>שישי</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>אנגלית ז (רביעי+חמישי, 2+2)</t>
+          <t>מתמטיקה ז (8 שעות, 2-3 ימים)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr"/>

--- a/מערכות שעות - לפי בתים.xlsx
+++ b/מערכות שעות - לפי בתים.xlsx
@@ -2677,9 +2677,9 @@
       <c r="A15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>מרים</t>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>אינס</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>אינס</t>
+          <t>מרים</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>ו שרית</t>
+          <t>ד אינס</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>ד אינס</t>
+          <t>ו שרית</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
@@ -12081,40 +12081,40 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>אנה זטרברג</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>אנה</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת א אנה</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="n">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>יערה שיכט</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>יערה</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>שני</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ב יערה</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J5" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="J5" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="K5" s="20" t="n">
-        <v>0</v>
+      <c r="K5" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -12159,96 +12159,96 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>יערה שיכט</t>
+          <t>אביטל בוארון</t>
         </is>
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>יערה</t>
+          <t>אביטל</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>שני</t>
+          <t>רביעי</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>מחנכת ב יערה</t>
+          <t>מחנכת ב אביטל</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>אביטל בוארון</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>אביטל</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>רביעי</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ב אביטל</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="J8" s="4" t="n">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>אנה זטרברג</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>אנה</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת א אנה</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="K8" s="4" t="n">
-        <v>2</v>
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="20" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
+      <c r="I8" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="J8" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="K8" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>אינס אלקבץ</t>
+          <t>סימה דוד</t>
         </is>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>אינס</t>
+          <t>סימה</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>שלישי</t>
+          <t>שישי</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>מחנכת ד אינס</t>
+          <t>יסודי</t>
         </is>
       </c>
       <c r="E9" s="20" t="n">
@@ -12270,22 +12270,22 @@
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>סימה דוד</t>
+          <t>אינס אלקבץ</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>סימה</t>
+          <t>אינס</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>שישי</t>
+          <t>שלישי</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>יסודי</t>
+          <t>מחנכת ד אינס</t>
         </is>
       </c>
       <c r="E10" s="20" t="n">
@@ -12385,22 +12385,22 @@
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>פנינה קרפטי</t>
+          <t>מירי בן עמי קריימר</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>פנינה</t>
+          <t>מירי</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>שני</t>
+          <t>חמישי</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>מחנכת א פנינה</t>
+          <t>מחנכת ד מירי</t>
         </is>
       </c>
       <c r="E13" s="20" t="n">
@@ -12420,116 +12420,118 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>מירי בן עמי קריימר</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>מירי</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ד מירי</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="n">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>לייה גור</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>לייה</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ג לייה · תנ"ך ח (כפול רצוף)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J14" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr"/>
-      <c r="H14" s="20" t="inlineStr"/>
-      <c r="I14" s="20" t="n">
+      <c r="K14" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>פנינה קרפטי</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>פנינה</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>שני</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת א פנינה</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="n">
         <v>23</v>
       </c>
-      <c r="J14" s="20" t="n">
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
+      <c r="I15" s="20" t="n">
         <v>23</v>
       </c>
-      <c r="K14" s="20" t="n">
+      <c r="J15" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="K15" s="20" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>לייה גור</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>לייה</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>רביעי</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ג לייה · תנ"ך ח (כפול רצוף)</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n">
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>אסיף בניש</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>אסיף</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>מחנך ט אסיף · שפה ט · מדעים ז · חינוך פיננסי ט · מגמת יזמות</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>דני יהב בראון</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>דני</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>שלישי</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>מחנך ה דני (20 שעות)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="n">
+      <c r="J16" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
-      <c r="H16" s="20" t="inlineStr"/>
-      <c r="I16" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="J16" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="K16" s="20" t="n">
-        <v>0</v>
+      <c r="K16" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -12570,40 +12572,40 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>נעמי קציר</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>נעמי</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="J18" s="4" t="n">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>דני יהב בראון</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>דני</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>מחנך ה דני (20 שעות)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="K18" s="4" t="n">
-        <v>5</v>
+      <c r="F18" s="20" t="inlineStr"/>
+      <c r="G18" s="20" t="inlineStr"/>
+      <c r="H18" s="20" t="inlineStr"/>
+      <c r="I18" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J18" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="K18" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -12648,22 +12650,22 @@
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>אסיף בניש</t>
+          <t>נעמי קציר</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>אסיף</t>
+          <t>נעמי</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>שישי</t>
+          <t>חמישי</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>מחנך ט אסיף · שפה ט · מדעים ז · חינוך פיננסי ט · מגמת יזמות</t>
+          <t>מחנכת ז נעמי · שפה ז+ח · ספרות ז+ח</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -12671,54 +12673,52 @@
         <v>15</v>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="n">
-        <v>4</v>
-      </c>
+      <c r="H20" s="4" t="inlineStr"/>
       <c r="I20" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>אורנה לוי</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>אורנה</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>שני, רביעי</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>מחנכת ו אורנה</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="J21" s="4" t="n">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>תניה דניאלי</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>תניה</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>מחנכת ה תניה (ראשון+רביעי מ-10:00)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="K21" s="4" t="n">
-        <v>1</v>
+      <c r="F21" s="20" t="inlineStr"/>
+      <c r="G21" s="20" t="inlineStr"/>
+      <c r="H21" s="20" t="inlineStr"/>
+      <c r="I21" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="J21" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="K21" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -12759,71 +12759,69 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>תניה דניאלי</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>תניה</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>חמישי</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>מחנכת ה תניה (ראשון+רביעי מ-10:00)</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="n">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>אורנה לוי</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>אורנה</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>שני, רביעי</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>מחנכת ו אורנה</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J23" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="F23" s="20" t="inlineStr"/>
-      <c r="G23" s="20" t="inlineStr"/>
-      <c r="H23" s="20" t="inlineStr"/>
-      <c r="I23" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="J23" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="K23" s="20" t="n">
-        <v>0</v>
+      <c r="K23" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>יעל ליפשיץ</t>
+          <t>הילית בן מאיר שטרן</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>יעל</t>
+          <t>הילית</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>חמישי, שישי</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>תל"ן בישול (ד-ו) · מגמה</t>
+          <t>תל"ן פיסול</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr"/>
       <c r="F24" s="20" t="inlineStr"/>
       <c r="G24" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="H24" s="20" t="n">
-        <v>4</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H24" s="20" t="inlineStr"/>
       <c r="I24" s="20" t="n">
         <v>16</v>
       </c>
@@ -12837,29 +12835,29 @@
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>פאני קרוטמן</t>
+          <t>יפעת גולדבלט</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>פאני</t>
+          <t>יפעת</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>שלישי</t>
+          <t>חמישי, שישי</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>ספורט יסודי (פעמיים בשבוע לכיתה, בימים שונים)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="n">
+          <t>תל"ן חינוך סביבתי</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr"/>
+      <c r="F25" s="20" t="inlineStr"/>
+      <c r="G25" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="F25" s="20" t="inlineStr"/>
-      <c r="G25" s="20" t="inlineStr"/>
       <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="n">
         <v>16</v>
@@ -12874,30 +12872,32 @@
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>יפעת גולדבלט</t>
+          <t>יעל ליפשיץ</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>יפעת</t>
+          <t>יעל</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>חמישי, שישי</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>תל"ן חינוך סביבתי</t>
+          <t>תל"ן בישול (ד-ו) · מגמה</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr"/>
       <c r="F26" s="20" t="inlineStr"/>
       <c r="G26" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="H26" s="20" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="H26" s="20" t="n">
+        <v>4</v>
+      </c>
       <c r="I26" s="20" t="n">
         <v>16</v>
       </c>
@@ -12911,29 +12911,29 @@
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>הילית בן מאיר שטרן</t>
+          <t>פאני קרוטמן</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>הילית</t>
+          <t>פאני</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>חמישי, שישי</t>
+          <t>שלישי</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>תל"ן פיסול</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="inlineStr"/>
+          <t>ספורט יסודי (פעמיים בשבוע לכיתה, בימים שונים)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>16</v>
+      </c>
       <c r="F27" s="20" t="inlineStr"/>
-      <c r="G27" s="20" t="n">
-        <v>16</v>
-      </c>
+      <c r="G27" s="20" t="inlineStr"/>
       <c r="H27" s="20" t="inlineStr"/>
       <c r="I27" s="20" t="n">
         <v>16</v>
@@ -13043,174 +13043,174 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>טלי ברינברג</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>טלי</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>יסודי (שני+שלישי בלבד)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>מאמי שימאזאקי</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>מאמי</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>מגמת אומנות בתנועה · רב מלל ח בחמישי 5-6</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>לי-אור שפירא</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>לי-אור</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>ראשון, רביעי, שישי</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>יסודי (עד 3 ימים)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F33" s="20" t="inlineStr"/>
+      <c r="G33" s="20" t="inlineStr"/>
+      <c r="H33" s="20" t="inlineStr"/>
+      <c r="I33" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="J33" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="K33" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>חגית אבידן</t>
         </is>
       </c>
-      <c r="B31" s="19" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>חגית</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>חמישי</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>תל"ן אומנות (א+ד) · מגמה</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr"/>
-      <c r="F31" s="20" t="inlineStr"/>
-      <c r="G31" s="20" t="n">
+      <c r="E34" s="20" t="inlineStr"/>
+      <c r="F34" s="20" t="inlineStr"/>
+      <c r="G34" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="H31" s="20" t="n">
+      <c r="H34" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="20" t="n">
+      <c r="I34" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="J31" s="20" t="n">
+      <c r="J34" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="K31" s="20" t="n">
+      <c r="K34" s="20" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>שחר שלייסר</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>שחר</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>ראשון, חמישי, שישי</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>יסודי (שני-רביעי, לא בשעה אחרונה)</t>
-        </is>
-      </c>
-      <c r="E32" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="F32" s="20" t="inlineStr"/>
-      <c r="G32" s="20" t="inlineStr"/>
-      <c r="H32" s="20" t="inlineStr"/>
-      <c r="I32" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="J32" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="K32" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>מאמי שימאזאקי</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>מאמי</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>מגמת אומנות בתנועה · רב מלל ח בחמישי 5-6</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>טלי ברינברג</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>טלי</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>יסודי (שני+שלישי בלבד)</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="4" t="inlineStr"/>
-      <c r="I34" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K34" s="4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>לי-אור שפירא</t>
+          <t>שחר שלייסר</t>
         </is>
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>לי-אור</t>
+          <t>שחר</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
         <is>
-          <t>ראשון, רביעי, שישי</t>
+          <t>ראשון, חמישי, שישי</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>יסודי (עד 3 ימים)</t>
+          <t>יסודי (שני-רביעי, לא בשעה אחרונה)</t>
         </is>
       </c>
       <c r="E35" s="20" t="n">
